--- a/test-files/gene-name-modifications/special-characters-tests/open-twirly-bracket-unrelated-input.xlsx
+++ b/test-files/gene-name-modifications/special-characters-tests/open-twirly-bracket-unrelated-input.xlsx
@@ -1,16 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="26505"/>
-  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihir/Documents/School/GRNsight/test-files/gene-name-modifications/special-characters-tests/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14160" tabRatio="759" firstSheet="6" activeTab="6"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false" showInkAnnotation="false"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
@@ -18,185 +9,45 @@
     <sheet name="log2_concentrations" sheetId="4" r:id="rId4"/>
     <sheet name="log2_optimized_concentrations" sheetId="5" r:id="rId5"/>
     <sheet name="degradation_rates" sheetId="6" r:id="rId6"/>
-    <sheet name="network" sheetId="9" r:id="rId7"/>
+    <sheet name="network" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="125725" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="47">
-  <si>
-    <t>SystematicName</t>
-  </si>
-  <si>
-    <t>StandardName</t>
-  </si>
-  <si>
-    <t>YKL112W</t>
-  </si>
-  <si>
-    <t>ABF1</t>
-  </si>
-  <si>
-    <t>YLR131C</t>
-  </si>
-  <si>
-    <t>ACE2</t>
-  </si>
-  <si>
-    <t>YGL071W</t>
-  </si>
-  <si>
-    <t>AFT1</t>
-  </si>
-  <si>
-    <t>YOR028C</t>
-  </si>
-  <si>
-    <t>CIN5</t>
-  </si>
-  <si>
-    <t>YPL177C</t>
-  </si>
-  <si>
-    <t>CUP9</t>
-  </si>
-  <si>
-    <t>YPR104C</t>
-  </si>
-  <si>
-    <t>FHL1</t>
-  </si>
-  <si>
-    <t>YGL181W</t>
-  </si>
-  <si>
-    <t>GTS1</t>
-  </si>
-  <si>
-    <t>YOL089C</t>
-  </si>
-  <si>
-    <t>HAL9</t>
-  </si>
-  <si>
-    <t>YGL073W</t>
-  </si>
-  <si>
-    <t>HSF1</t>
-  </si>
-  <si>
-    <t>YMR021C</t>
-  </si>
-  <si>
-    <t>MAC1</t>
-  </si>
-  <si>
-    <t>YOL116W</t>
-  </si>
-  <si>
-    <t>MSN1</t>
-  </si>
-  <si>
-    <t>YKL062W</t>
-  </si>
-  <si>
-    <t>MSN4</t>
-  </si>
-  <si>
-    <t>YDR043C</t>
-  </si>
-  <si>
-    <t>NRG1</t>
-  </si>
-  <si>
-    <t>YKL043W</t>
-  </si>
-  <si>
-    <t>PHD1</t>
-  </si>
-  <si>
-    <t>YNL216W</t>
-  </si>
-  <si>
-    <t>RAP1</t>
-  </si>
-  <si>
-    <t>YBR049C</t>
-  </si>
-  <si>
-    <t>REB1</t>
-  </si>
-  <si>
-    <t>YPR065W</t>
-  </si>
-  <si>
-    <t>ROX1</t>
-  </si>
-  <si>
-    <t>YER169W</t>
-  </si>
-  <si>
-    <t>RPH1</t>
-  </si>
-  <si>
-    <t>YHR206W</t>
-  </si>
-  <si>
-    <t>SKN7</t>
-  </si>
-  <si>
-    <t>YML007W</t>
-  </si>
-  <si>
-    <t>YAP1</t>
-  </si>
-  <si>
-    <t>YDR259C</t>
-  </si>
-  <si>
-    <t>YAP6</t>
-  </si>
-  <si>
-    <t>DegradationRate</t>
-  </si>
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>ABF1{</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -216,38 +67,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="9">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -572,43 +402,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>15</v>
@@ -620,29 +455,29 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
-        <v>-1.1802129985963199</v>
+        <v>-1.18021299859632</v>
       </c>
       <c r="D2">
         <v>-1.35534786374789</v>
       </c>
       <c r="E2">
-        <v>-2.2843447109758301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>-2.28434471097583</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>-0.168317226797601</v>
@@ -651,219 +486,219 @@
         <v>0.159981381075125</v>
       </c>
       <c r="E3">
-        <v>-8.4072251269262696E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>-0.0840722512692627</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
         <v>0.110916570402342</v>
       </c>
       <c r="D4">
-        <v>0.34518552113600498</v>
+        <v>0.345185521136005</v>
       </c>
       <c r="E4">
-        <v>0.29611171632314098</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>0.296111716323141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>0.57398886351082801</v>
+        <v>0.573988863510828</v>
       </c>
       <c r="D5">
-        <v>0.90044244474717405</v>
+        <v>0.900442444747174</v>
       </c>
       <c r="E5">
         <v>1.75845186354745</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
-        <v>-0.34976006979129598</v>
+        <v>-0.349760069791296</v>
       </c>
       <c r="D6">
-        <v>-0.97753185452394098</v>
+        <v>-0.977531854523941</v>
       </c>
       <c r="E6">
-        <v>-0.76236366760055096</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>-0.762363667600551</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>-4.4276309137313001E-2</v>
+        <v>-0.044276309137313</v>
       </c>
       <c r="D7">
-        <v>0.24181613073483699</v>
+        <v>0.241816130734837</v>
       </c>
       <c r="E7">
-        <v>0.62853290835895503</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.628532908358955</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>-0.220356822259166</v>
       </c>
       <c r="D8">
-        <v>-0.11669113002233999</v>
+        <v>-0.11669113002234</v>
       </c>
       <c r="E8">
-        <v>-8.7143718210927298E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>-0.0871437182109273</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>-0.16064769982257401</v>
+        <v>-0.160647699822574</v>
       </c>
       <c r="D9">
-        <v>0.20886614963405101</v>
+        <v>0.208866149634051</v>
       </c>
       <c r="E9">
-        <v>0.84698244904192099</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.846982449041921</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>-0.97765022692802495</v>
+        <v>-0.977650226928025</v>
       </c>
       <c r="D10">
-        <v>-1.1044654053835501</v>
+        <v>-1.10446540538355</v>
       </c>
       <c r="E10">
-        <v>-0.73218305564943398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+        <v>-0.732183055649434</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>0.61308674677972397</v>
+        <v>0.613086746779724</v>
       </c>
       <c r="D11">
-        <v>0.49022096483014099</v>
+        <v>0.490220964830141</v>
       </c>
       <c r="E11">
-        <v>0.45176478094112998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.45176478094113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
         <v>0.124182913442922</v>
       </c>
       <c r="D12">
-        <v>-0.42545856172641699</v>
+        <v>-0.425458561726417</v>
       </c>
       <c r="E12">
-        <v>-0.48116619434522001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>-0.48116619434522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>0.98300627566904297</v>
+        <v>0.983006275669043</v>
       </c>
       <c r="D13">
         <v>0.976858174028987</v>
       </c>
       <c r="E13">
-        <v>1.4416179829439899</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>1.44161798294399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>-0.75199845082126104</v>
+        <v>-0.751998450821261</v>
       </c>
       <c r="D14">
-        <v>-0.39598482761536302</v>
+        <v>-0.395984827615363</v>
       </c>
       <c r="E14">
-        <v>-0.29043031142040199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>-0.290430311420402</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>0.40478070501389601</v>
+        <v>0.404780705013896</v>
       </c>
       <c r="D15">
-        <v>0.63962144886654104</v>
+        <v>0.639621448866541</v>
       </c>
       <c r="E15">
-        <v>0.41039596022329999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.4103959602233</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>-1.41026384750747</v>
@@ -872,32 +707,32 @@
         <v>-0.269044364431755</v>
       </c>
       <c r="E16">
-        <v>9.0586658239791298E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.0905866582397913</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
         <v>-0.105709302884452</v>
       </c>
       <c r="D17">
-        <v>-0.25108884778781598</v>
+        <v>-0.251088847787816</v>
       </c>
       <c r="E17">
-        <v>-0.19878651280399501</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>-0.198786512803995</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
         <v>-1.02661929129623</v>
@@ -906,93 +741,95 @@
         <v>-1.26262750699747</v>
       </c>
       <c r="E18">
-        <v>-1.1921015273515501</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>-1.19210152735155</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
-        <v>1.3177110283620199</v>
+        <v>1.31771102836202</v>
       </c>
       <c r="D19">
-        <v>1.2880472692047999</v>
+        <v>1.2880472692048</v>
       </c>
       <c r="E19">
-        <v>1.5309831587774501</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>1.53098315877745</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
-        <v>0.40820898095417801</v>
+        <v>0.408208980954178</v>
       </c>
       <c r="D20">
-        <v>1.0500276907448201</v>
+        <v>1.05002769074482</v>
       </c>
       <c r="E20">
-        <v>1.4171295501935499</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>1.41712955019355</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>1.4028761460241701</v>
+        <v>1.40287614602417</v>
       </c>
       <c r="D21">
-        <v>1.2314519660749701</v>
+        <v>1.23145196607497</v>
       </c>
       <c r="E21">
         <v>1.50806209670647</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>-0.66486605652808095</v>
+        <v>-0.664866056528081</v>
       </c>
       <c r="D22">
-        <v>-0.51022603008343204</v>
+        <v>-0.510226030083432</v>
       </c>
       <c r="E22">
-        <v>-0.72124064515279496</v>
+        <v>-0.721240645152795</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>0</v>
@@ -1016,12 +853,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1045,12 +882,12 @@
         <v>-1.614737262334736</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1059,27 +896,27 @@
         <v>-0.11040395846978003</v>
       </c>
       <c r="E3">
-        <v>-2.9294442228075389E-2</v>
+        <v>-0.02929444222807539</v>
       </c>
       <c r="F3">
-        <v>2.1655862491403277E-2</v>
+        <v>0.021655862491403277</v>
       </c>
       <c r="G3">
-        <v>3.2684625886707508E-2</v>
+        <v>0.03268462588670751</v>
       </c>
       <c r="H3">
-        <v>9.1545307598435155E-3</v>
+        <v>0.009154530759843515</v>
       </c>
       <c r="I3">
-        <v>-4.4152407880423003E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>-0.044152407880423</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1103,21 +940,21 @@
         <v>0.34245532652126665</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.46687949602312651</v>
+        <v>0.4668794960231265</v>
       </c>
       <c r="E5">
-        <v>0.82854334589694734</v>
+        <v>0.8285433458969473</v>
       </c>
       <c r="F5">
         <v>1.1029505278199978</v>
@@ -1132,12 +969,12 @@
         <v>1.5632943329859523</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1149,30 +986,30 @@
         <v>-0.41982200384813556</v>
       </c>
       <c r="F6">
-        <v>-0.59438769830819549</v>
+        <v>-0.5943876983081955</v>
       </c>
       <c r="G6">
-        <v>-0.74559260039639175</v>
+        <v>-0.7455926003963917</v>
       </c>
       <c r="H6">
-        <v>-0.87450332011299015</v>
+        <v>-0.8745033201129901</v>
       </c>
       <c r="I6">
-        <v>-0.98278112783760696</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>-0.982781127837607</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>3.1002632793568075E-2</v>
+        <v>0.031002632793568075</v>
       </c>
       <c r="E7">
         <v>0.10232516759231325</v>
@@ -1181,33 +1018,33 @@
         <v>0.20795344348503297</v>
       </c>
       <c r="G7">
-        <v>0.33684734635395208</v>
+        <v>0.3368473463539521</v>
       </c>
       <c r="H7">
-        <v>0.47630626960413769</v>
+        <v>0.4763062696041377</v>
       </c>
       <c r="I7">
-        <v>0.61518119934801141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.6151811993480114</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>-5.2283146832533892E-2</v>
+        <v>-0.05228314683253389</v>
       </c>
       <c r="E8">
-        <v>-8.1046704126378807E-2</v>
+        <v>-0.08104670412637881</v>
       </c>
       <c r="F8">
-        <v>-9.9142665384753567E-2</v>
+        <v>-0.09914266538475357</v>
       </c>
       <c r="G8">
         <v>-0.11258114499318174</v>
@@ -1219,18 +1056,18 @@
         <v>-0.134864828008146</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.17433130892865101</v>
+        <v>0.174331308928651</v>
       </c>
       <c r="E9">
         <v>0.29432882513778413</v>
@@ -1245,73 +1082,73 @@
         <v>0.48648768078802895</v>
       </c>
       <c r="I9">
-        <v>0.52007384366239306</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.5200738436623931</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>-0.25176748621007727</v>
+        <v>-0.2517674862100773</v>
       </c>
       <c r="E10">
         <v>-0.47825711897799816</v>
       </c>
       <c r="F10">
-        <v>-0.67838972936630726</v>
+        <v>-0.6783897293663073</v>
       </c>
       <c r="G10">
         <v>-0.8520175600464891</v>
       </c>
       <c r="H10">
-        <v>-0.99994496786797782</v>
+        <v>-0.9999449678679778</v>
       </c>
       <c r="I10">
         <v>-1.1238172749525641</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.30052947798808971</v>
+        <v>0.3005294779880897</v>
       </c>
       <c r="E11">
         <v>0.46876122780688256</v>
       </c>
       <c r="F11">
-        <v>0.56092296453642465</v>
+        <v>0.5609229645364247</v>
       </c>
       <c r="G11">
-        <v>0.60680401465925349</v>
+        <v>0.6068040146592535</v>
       </c>
       <c r="H11">
         <v>0.6238713196777923</v>
       </c>
       <c r="I11">
-        <v>0.62289346498752207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.6228934649875221</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1326,7 +1163,7 @@
         <v>-0.31478044020549834</v>
       </c>
       <c r="G12">
-        <v>-0.35892415573528641</v>
+        <v>-0.3589241557352864</v>
       </c>
       <c r="H12">
         <v>-0.3872323500604975</v>
@@ -1335,21 +1172,21 @@
         <v>-0.40518417542879076</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0.70649152174107299</v>
+        <v>0.706491521741073</v>
       </c>
       <c r="E13">
-        <v>0.98007232509393927</v>
+        <v>0.9800723250939393</v>
       </c>
       <c r="F13">
         <v>1.132635255942561</v>
@@ -1364,12 +1201,12 @@
         <v>1.3857553092197141</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1378,27 +1215,27 @@
         <v>-0.39341967139404665</v>
       </c>
       <c r="E14">
-        <v>-0.53314369637685366</v>
+        <v>-0.5331436963768537</v>
       </c>
       <c r="F14">
-        <v>-0.52221178459618123</v>
+        <v>-0.5222117845961812</v>
       </c>
       <c r="G14">
-        <v>-0.45413546318994757</v>
+        <v>-0.4541354631899476</v>
       </c>
       <c r="H14">
-        <v>-0.38056549415676622</v>
+        <v>-0.3805654941567662</v>
       </c>
       <c r="I14">
         <v>-0.32348780752512174</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1407,27 +1244,27 @@
         <v>0.2653416822590543</v>
       </c>
       <c r="E15">
-        <v>0.42297857607446532</v>
+        <v>0.4229785760744653</v>
       </c>
       <c r="F15">
-        <v>0.51951059951922429</v>
+        <v>0.5195105995192243</v>
       </c>
       <c r="G15">
-        <v>0.57454163987868734</v>
+        <v>0.5745416398786873</v>
       </c>
       <c r="H15">
-        <v>0.59715888711940535</v>
+        <v>0.5971588871194053</v>
       </c>
       <c r="I15">
-        <v>0.59223490664700296</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.592234906647003</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1439,24 +1276,24 @@
         <v>-0.3528618636829009</v>
       </c>
       <c r="F16">
-        <v>-0.40633787751804529</v>
+        <v>-0.4063378775180453</v>
       </c>
       <c r="G16">
-        <v>-0.34102289103002359</v>
+        <v>-0.3410228910300236</v>
       </c>
       <c r="H16">
         <v>-0.16841750409254783</v>
       </c>
       <c r="I16">
-        <v>7.2760038315940578E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.07276003831594058</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1480,12 +1317,12 @@
         <v>-0.2313321871712328</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1494,33 +1331,33 @@
         <v>-0.19230769239818427</v>
       </c>
       <c r="E18">
-        <v>-0.38461538477984047</v>
+        <v>-0.3846153847798405</v>
       </c>
       <c r="F18">
         <v>-0.5769230773051045</v>
       </c>
       <c r="G18">
-        <v>-0.76923077163695375</v>
+        <v>-0.7692307716369537</v>
       </c>
       <c r="H18">
-        <v>-0.96153846213095273</v>
+        <v>-0.9615384621309527</v>
       </c>
       <c r="I18">
         <v>-1.153846153117154</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0.75834215916691061</v>
+        <v>0.7583421591669106</v>
       </c>
       <c r="E19">
         <v>1.1492776094069987</v>
@@ -1538,24 +1375,24 @@
         <v>1.7594447626156464</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0.41819827528874198</v>
+        <v>0.418198275288742</v>
       </c>
       <c r="E20">
-        <v>0.72807837034630563</v>
+        <v>0.7280783703463056</v>
       </c>
       <c r="F20">
-        <v>0.96261817285065654</v>
+        <v>0.9626181728506565</v>
       </c>
       <c r="G20">
         <v>1.141604658886969</v>
@@ -1567,12 +1404,12 @@
         <v>1.3835119382868828</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1590,18 +1427,18 @@
         <v>1.4602353276095015</v>
       </c>
       <c r="H21">
-        <v>1.4600786980962801</v>
+        <v>1.46007869809628</v>
       </c>
       <c r="I21">
         <v>1.4505220392146478</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1610,354 +1447,358 @@
         <v>-0.21851818757772912</v>
       </c>
       <c r="E22">
-        <v>-0.39895304188761599</v>
+        <v>-0.398953041887616</v>
       </c>
       <c r="F22">
-        <v>-0.54419485659236189</v>
+        <v>-0.5441948565923619</v>
       </c>
       <c r="G22">
         <v>-0.658449045182813</v>
       </c>
       <c r="H22">
-        <v>-0.74655983141691495</v>
+        <v>-0.746559831416915</v>
       </c>
       <c r="I22">
-        <v>-0.81339923703166106</v>
+        <v>-0.8133992370316611</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>DegradationRate</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>0.34657359027997264</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>0.23104906018664842</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
-        <v>2.5672117798516494E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>0.025672117798516494</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>1.7328679513998631E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.01732867951399863</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
-        <v>1.1002336199364211E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>0.01100233619936421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>7.453195489891885E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.007453195489891885</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
-        <v>7.7016353395549478E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>0.07701635339554948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>6.9314718055994526E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>0.06931471805599453</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>4.9510512897138946E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.049510512897138946</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
-        <v>1.6503504299046318E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.016503504299046318</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
-        <v>5.7762265046662105E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>0.057762265046662105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
-        <v>1.332975347230664E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>0.01332975347230664</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
-        <v>1.2602676010180823E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>0.012602676010180823</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>3.3007008598092635E-2</v>
+        <v>0.033007008598092635</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>46</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ABF1{</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>AFT1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CUP9</v>
+      </c>
+      <c r="G1" t="str">
+        <v>FHL1</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GTS1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HAL9</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HSF1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MAC1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MSN1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NRG1</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PHD1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>RAP1</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>REB1</v>
+      </c>
+      <c r="R1" t="str">
+        <v>ROX1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>RPH1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SKN7</v>
+      </c>
+      <c r="U1" t="str">
+        <v>YAP1</v>
+      </c>
+      <c r="V1" t="str">
+        <v>YAP6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ABF1{</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2023,9 +1864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2091,9 +1932,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2159,9 +2000,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2227,9 +2068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2295,9 +2136,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2363,9 +2204,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>15</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2431,9 +2272,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2499,9 +2340,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>19</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2567,9 +2408,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2635,9 +2476,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>23</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2703,9 +2544,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2771,9 +2612,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2839,9 +2680,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2907,9 +2748,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2975,9 +2816,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>33</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>REB1</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3043,9 +2884,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3111,9 +2952,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>37</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3179,9 +3020,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3247,9 +3088,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3315,9 +3156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3384,7 +3225,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V22"/>
+  </ignoredErrors>
 </worksheet>
 </file>